--- a/data/explorer_outputs.xlsx
+++ b/data/explorer_outputs.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -685,6 +685,336 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:04:27</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Find stocks where RSI is below 30 and close is above 50 day moving average</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>RSI Below 30 Above MA50</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Finds stocks where RSI is below 30 and the close is above the 50-day moving average. Assumes RSI uses the default 14-period RSI and the moving average is simple because no method was specified.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>RSI(14) &lt; 30 AND C &gt; Mov(C,50,S)</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>[{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "RSI(14)"}, {"col_letter": "C", "col_code": "Mov(C,50,S)"}]</t>
+        </is>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>{"explorer_name": "RSI Below 30 Above MA50", "explorer_description": "Finds stocks where RSI is below 30 and the close is above the 50-day moving average. Assumes RSI uses the default 14-period RSI and the moving average is simple because no method was specified.", "explorer_code_body": "RSI(14) &lt; 30 AND C &gt; Mov(C,50,S)", "col_definitions": [{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "RSI(14)"}, {"col_letter": "C", "col_code": "Mov(C,50,S)"}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:06:34</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Find stocks where RSI is below 30 and close is above 50 day moving average</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>RSI Below 30 Above MA50</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Finds stocks where RSI is below 30 and the close is above the 50-day moving average. Assumes RSI uses the default 14-period setting and the moving average is simple.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>RSI(14) &lt; 30 AND C &gt; Mov(C,50,S)</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>[{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "RSI(14)"}, {"col_letter": "C", "col_code": "Mov(C,50,S)"}]</t>
+        </is>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>{"explorer_name": "RSI Below 30 Above MA50", "explorer_description": "Finds stocks where RSI is below 30 and the close is above the 50-day moving average. Assumes RSI uses the default 14-period setting and the moving average is simple.", "explorer_code_body": "RSI(14) &lt; 30 AND C &gt; Mov(C,50,S)", "col_definitions": [{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "RSI(14)"}, {"col_letter": "C", "col_code": "Mov(C,50,S)"}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:08:41</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Find stocks where RSI is below 30 and close is above 50 day moving average</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RSI Below 30 Above MA50</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Finds stocks where RSI is below 30 and the close is above the 50-day moving average. Assumes RSI uses the default 14-period setting and the moving average is simple.</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>RSI(14) &lt; 30 AND C &gt; Mov(C,50,S)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>[{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "RSI(14)"}, {"col_letter": "C", "col_code": "Mov(C,50,S)"}]</t>
+        </is>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>{"explorer_name": "RSI Below 30 Above MA50", "explorer_description": "Finds stocks where RSI is below 30 and the close is above the 50-day moving average. Assumes RSI uses the default 14-period setting and the moving average is simple.", "explorer_code_body": "RSI(14) &lt; 30 AND C &gt; Mov(C,50,S)", "col_definitions": [{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "RSI(14)"}, {"col_letter": "C", "col_code": "Mov(C,50,S)"}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:16:19</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Find stocks where RSI is below 30 and close is above 50 day moving average</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RSI Below 30 Above MA50</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Finds stocks where RSI is below 30 and the close is above the 50-day moving average. Assumes RSI uses the default 14-period setting and the moving average is simple.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>RSI(14) &lt; 30 AND C &gt; Mov(C,50,S)</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>[{"col_code": "C", "col_letter": "A"}, {"col_code": "RSI(14)", "col_letter": "B"}, {"col_code": "Mov(C,50,S)", "col_letter": "C"}]</t>
+        </is>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>{"explorer_name": "RSI Below 30 Above MA50", "col_definitions": [{"col_code": "C", "col_letter": "A"}, {"col_code": "RSI(14)", "col_letter": "B"}, {"col_code": "Mov(C,50,S)", "col_letter": "C"}], "explorer_code_body": "RSI(14) &lt; 30 AND C &gt; Mov(C,50,S)", "explorer_description": "Finds stocks where RSI is below 30 and the close is above the 50-day moving average. Assumes RSI uses the default 14-period setting and the moving average is simple."}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:22:15</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Find stocks where RSI is below 30 and close is above 50 day moving average</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>RSI Below 30 Above MA50</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Finds stocks where RSI is below 30 and the close is above the 50-day moving average. Assumes RSI uses the default 14-period setting and the moving average is simple.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>RSI(14) &lt; 30 AND C &gt; Mov(C,50,S)</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>[{"col_code": "C", "col_letter": "A"}, {"col_code": "RSI(14)", "col_letter": "B"}, {"col_code": "Mov(C,50,S)", "col_letter": "C"}]</t>
+        </is>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>{"explorer_name": "RSI Below 30 Above MA50", "col_definitions": [{"col_code": "C", "col_letter": "A"}, {"col_code": "RSI(14)", "col_letter": "B"}, {"col_code": "Mov(C,50,S)", "col_letter": "C"}], "explorer_code_body": "RSI(14) &lt; 30 AND C &gt; Mov(C,50,S)", "explorer_description": "Finds stocks where RSI is below 30 and the close is above the 50-day moving average. Assumes RSI uses the default 14-period setting and the moving average is simple."}</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-06-02T17:23:05</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>“Find stocks where RSI is below 30 and close is above 50 day moving average”</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RSI Below 30 Above MA50</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Finds stocks where RSI is below 30 and the close is above the 50-day moving average. Assumes RSI uses the default 14-period setting and the 50-day moving average is simple.</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>RSI(14) &lt; 30 AND C &gt; Mov(C,50,S)</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>[{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "RSI(14)"}, {"col_letter": "C", "col_code": "Mov(C,50,S)"}]</t>
+        </is>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>{"explorer_name": "RSI Below 30 Above MA50", "explorer_description": "Finds stocks where RSI is below 30 and the close is above the 50-day moving average. Assumes RSI uses the default 14-period setting and the 50-day moving average is simple.", "explorer_code_body": "RSI(14) &lt; 30 AND C &gt; Mov(C,50,S)", "col_definitions": [{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "RSI(14)"}, {"col_letter": "C", "col_code": "Mov(C,50,S)"}]}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/explorer_outputs.xlsx
+++ b/data/explorer_outputs.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1015,6 +1015,61 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-06-16T18:03:06</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Find stocks where the LLV is 2 times lower than the HHV, RSI is below 20 and close is above 20 day moving average</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>LLV Half HHV RSI MA</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Finds stocks where the 20-period lowest low is at most half of the 20-period highest high, RSI(14) is below 20, and the close is above the 20-day simple moving average. Assumes LLV uses L, HHV uses H, RSI defaults to 14 periods, and moving average defaults to simple.</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>LLV(L,20) &lt;= HHV(H,20) / 2 AND RSI(14) &lt; 20 AND C &gt; Mov(C,20,S)</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>[{"col_letter": "A", "col_code": "LLV(L,20)"}, {"col_letter": "B", "col_code": "HHV(H,20)"}, {"col_letter": "C", "col_code": "RSI(14)"}, {"col_letter": "D", "col_code": "C"}, {"col_letter": "E", "col_code": "Mov(C,20,S)"}]</t>
+        </is>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>{"explorer_name": "LLV Half HHV RSI MA", "explorer_description": "Finds stocks where the 20-period lowest low is at most half of the 20-period highest high, RSI(14) is below 20, and the close is above the 20-day simple moving average. Assumes LLV uses L, HHV uses H, RSI defaults to 14 periods, and moving average defaults to simple.", "explorer_code_body": "LLV(L,20) &lt;= HHV(H,20) / 2 AND RSI(14) &lt; 20 AND C &gt; Mov(C,20,S)", "col_definitions": [{"col_letter": "A", "col_code": "LLV(L,20)"}, {"col_letter": "B", "col_code": "HHV(H,20)"}, {"col_letter": "C", "col_code": "RSI(14)"}, {"col_letter": "D", "col_code": "C"}, {"col_letter": "E", "col_code": "Mov(C,20,S)"}]}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/explorer_outputs.xlsx
+++ b/data/explorer_outputs.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1015,61 +1015,6 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-06-16T18:03:06</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>openai</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>gpt-5.5</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Find stocks where the LLV is 2 times lower than the HHV, RSI is below 20 and close is above 20 day moving average</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>LLV Half HHV RSI MA</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Finds stocks where the 20-period lowest low is at most half of the 20-period highest high, RSI(14) is below 20, and the close is above the 20-day simple moving average. Assumes LLV uses L, HHV uses H, RSI defaults to 14 periods, and moving average defaults to simple.</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>LLV(L,20) &lt;= HHV(H,20) / 2 AND RSI(14) &lt; 20 AND C &gt; Mov(C,20,S)</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>[{"col_letter": "A", "col_code": "LLV(L,20)"}, {"col_letter": "B", "col_code": "HHV(H,20)"}, {"col_letter": "C", "col_code": "RSI(14)"}, {"col_letter": "D", "col_code": "C"}, {"col_letter": "E", "col_code": "Mov(C,20,S)"}]</t>
-        </is>
-      </c>
-      <c r="I11" t="b">
-        <v>1</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>{"explorer_name": "LLV Half HHV RSI MA", "explorer_description": "Finds stocks where the 20-period lowest low is at most half of the 20-period highest high, RSI(14) is below 20, and the close is above the 20-day simple moving average. Assumes LLV uses L, HHV uses H, RSI defaults to 14 periods, and moving average defaults to simple.", "explorer_code_body": "LLV(L,20) &lt;= HHV(H,20) / 2 AND RSI(14) &lt; 20 AND C &gt; Mov(C,20,S)", "col_definitions": [{"col_letter": "A", "col_code": "LLV(L,20)"}, {"col_letter": "B", "col_code": "HHV(H,20)"}, {"col_letter": "C", "col_code": "RSI(14)"}, {"col_letter": "D", "col_code": "C"}, {"col_letter": "E", "col_code": "Mov(C,20,S)"}]}</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/explorer_outputs.xlsx
+++ b/data/explorer_outputs.xlsx
@@ -444,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1070,6 +1070,611 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-07T10:25:43</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Find stocks where Bollinger Bands have contracted into a squeeze, price closes above the upper Bollinger Band, RSI shows bullish divergence, and the formula should avoid lookahead or head-fake style false breakout logic</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>BB Squeeze RSI Div Breakout</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Finds stocks with a Bollinger Band squeeze where current band width is below its 50-period simple average, the close is above the upper Bollinger Band, RSI(14) shows positive divergence using Divergence(RSI(14),C,5), and volume is above its 20-period average as confirmation to reduce head-fake breakouts. Assumes default Bollinger settings C,20,S,2, RSI period 14, and 5 percent Divergence swings. The filter avoids future references/lookahead; however MetaStock Divergence is ZigZag-based, so its most recent signal can change.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>(BBandTop(C,20,S,2)-BBandBot(C,20,S,2)) &lt; Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S) AND C &gt; BBandTop(C,20,S,2) AND Divergence(RSI(14),C,5) &gt; 0 AND V &gt; Mov(V,20,S)</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>[{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "BBandTop(C,20,S,2)"}, {"col_letter": "C", "col_code": "BBandBot(C,20,S,2)"}, {"col_letter": "D", "col_code": "BBandTop(C,20,S,2)-BBandBot(C,20,S,2)"}, {"col_letter": "E", "col_code": "Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S)"}, {"col_letter": "F", "col_code": "RSI(14)"}, {"col_letter": "G", "col_code": "Divergence(RSI(14),C,5)"}, {"col_letter": "H", "col_code": "V"}, {"col_letter": "I", "col_code": "Mov(V,20,S)"}]</t>
+        </is>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>["explorer_code_body: Function may be unsupported or missing from whitelist: BBandTop", "explorer_code_body: Function may be unsupported or missing from whitelist: BBandBot", "explorer_code_body: Function may be unsupported or missing from whitelist: BBandTop", "explorer_code_body: Function may be unsupported or missing from whitelist: BBandBot", "explorer_code_body: Function may be unsupported or missing from whitelist: BBandTop", "explorer_code_body: Function may be unsupported or missing from whitelist: Divergence", "col B: Function may be unsupported or missing from whitelist: BBandTop", "col C: Function may be unsupported or missing from whitelist: BBandBot", "col D: Function may be unsupported or missing from whitelist: BBandTop", "col D: Function may be unsupported or missing from whitelist: BBandBot", "col E: Function may be unsupported or missing from whitelist: BBandTop", "col E: Function may be unsupported or missing from whitelist: BBandBot", "col G: Function may be unsupported or missing from whitelist: Divergence"]</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>{"explorer_name": "BB Squeeze RSI Div Breakout", "explorer_description": "Finds stocks with a Bollinger Band squeeze where current band width is below its 50-period simple average, the close is above the upper Bollinger Band, RSI(14) shows positive divergence using Divergence(RSI(14),C,5), and volume is above its 20-period average as confirmation to reduce head-fake breakouts. Assumes default Bollinger settings C,20,S,2, RSI period 14, and 5 percent Divergence swings. The filter avoids future references/lookahead; however MetaStock Divergence is ZigZag-based, so its most recent signal can change.", "explorer_code_body": "(BBandTop(C,20,S,2)-BBandBot(C,20,S,2)) &lt; Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S) AND C &gt; BBandTop(C,20,S,2) AND Divergence(RSI(14),C,5) &gt; 0 AND V &gt; Mov(V,20,S)", "col_definitions": [{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "BBandTop(C,20,S,2)"}, {"col_letter": "C", "col_code": "BBandBot(C,20,S,2)"}, {"col_letter": "D", "col_code": "BBandTop(C,20,S,2)-BBandBot(C,20,S,2)"}, {"col_letter": "E", "col_code": "Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S)"}, {"col_letter": "F", "col_code": "RSI(14)"}, {"col_letter": "G", "col_code": "Divergence(RSI(14),C,5)"}, {"col_letter": "H", "col_code": "V"}, {"col_letter": "I", "col_code": "Mov(V,20,S)"}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-07T10:33:32</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Find stocks where Bollinger Bands have contracted into a squeeze, price closes above the upper Bollinger Band, RSI shows bullish divergence, and the formula should avoid lookahead or head-fake style false breakout logic</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>BB Squeeze RSI Div Breakout</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Finds stocks in a Bollinger Band squeeze where the close is above the upper Bollinger Band, a recent fixed-window bullish RSI divergence occurred, and volume is above its 20-period average to help reduce head-fake breakouts. Assumptions: Bollinger Bands use C,20,S,2; squeeze means band width is below its 50-period simple average; RSI uses 14 periods; bullish RSI divergence uses a no-lookahead 20-period fixed-window approximation and must have occurred within the last 10 bars.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>(BBandTop(C,20,S,2)-BBandBot(C,20,S,2)) &lt; Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S) AND C &gt; BBandTop(C,20,S,2) AND BarsSince(C &lt; Ref(LLV(C,20),-1) AND RSI(14) &gt; Ref(LLV(RSI(14),20),-1)) &lt; 10 AND V &gt; Mov(V,20,S)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>[{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "BBandTop(C,20,S,2)"}, {"col_letter": "C", "col_code": "BBandBot(C,20,S,2)"}, {"col_letter": "D", "col_code": "BBandTop(C,20,S,2)-BBandBot(C,20,S,2)"}, {"col_letter": "E", "col_code": "Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S)"}, {"col_letter": "F", "col_code": "RSI(14)"}, {"col_letter": "G", "col_code": "Ref(LLV(C,20),-1)"}, {"col_letter": "H", "col_code": "Ref(LLV(RSI(14),20),-1)"}, {"col_letter": "I", "col_code": "BarsSince(C &lt; Ref(LLV(C,20),-1) AND RSI(14) &gt; Ref(LLV(RSI(14),20),-1))"}, {"col_letter": "J", "col_code": "V"}, {"col_letter": "K", "col_code": "Mov(V,20,S)"}]</t>
+        </is>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>["explorer_code_body: Positive Ref(...,+N) / Ref(...,N) appears to reference future data. Use negative periods such as Ref(C,-1) for previous bars in Explorer.", "col G: Positive Ref(...,+N) / Ref(...,N) appears to reference future data. Use negative periods such as Ref(C,-1) for previous bars in Explorer.", "col H: Positive Ref(...,+N) / Ref(...,N) appears to reference future data. Use negative periods such as Ref(C,-1) for previous bars in Explorer.", "col I: Positive Ref(...,+N) / Ref(...,N) appears to reference future data. Use negative periods such as Ref(C,-1) for previous bars in Explorer."]</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>{"explorer_name": "BB Squeeze RSI Div Breakout", "explorer_description": "Finds stocks in a Bollinger Band squeeze where the close is above the upper Bollinger Band, a recent fixed-window bullish RSI divergence occurred, and volume is above its 20-period average to help reduce head-fake breakouts. Assumptions: Bollinger Bands use C,20,S,2; squeeze means band width is below its 50-period simple average; RSI uses 14 periods; bullish RSI divergence uses a no-lookahead 20-period fixed-window approximation and must have occurred within the last 10 bars.", "explorer_code_body": "(BBandTop(C,20,S,2)-BBandBot(C,20,S,2)) &lt; Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S) AND C &gt; BBandTop(C,20,S,2) AND BarsSince(C &lt; Ref(LLV(C,20),-1) AND RSI(14) &gt; Ref(LLV(RSI(14),20),-1)) &lt; 10 AND V &gt; Mov(V,20,S)", "col_definitions": [{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "BBandTop(C,20,S,2)"}, {"col_letter": "C", "col_code": "BBandBot(C,20,S,2)"}, {"col_letter": "D", "col_code": "BBandTop(C,20,S,2)-BBandBot(C,20,S,2)"}, {"col_letter": "E", "col_code": "Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S)"}, {"col_letter": "F", "col_code": "RSI(14)"}, {"col_letter": "G", "col_code": "Ref(LLV(C,20),-1)"}, {"col_letter": "H", "col_code": "Ref(LLV(RSI(14),20),-1)"}, {"col_letter": "I", "col_code": "BarsSince(C &lt; Ref(LLV(C,20),-1) AND RSI(14) &gt; Ref(LLV(RSI(14),20),-1))"}, {"col_letter": "J", "col_code": "V"}, {"col_letter": "K", "col_code": "Mov(V,20,S)"}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-07T10:36:53</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Find stocks where Bollinger Bands have contracted into a squeeze, price closes above the upper Bollinger Band, RSI shows bullish divergence, and the formula should avoid lookahead or head-fake style false breakout logic</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>BB Squeeze RSI Div Breakout</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Finds stocks with a Bollinger Band squeeze and a close-confirmed breakout above the upper Bollinger Band. Assumptions: default Bollinger settings are C,20,S,2; squeeze means band width is below its 50-period simple average; RSI uses RSI(14); bullish RSI divergence is approximated with prior-bar fixed-window logic, where the prior close made a lower low versus the preceding 20-period close low while prior RSI stayed above its preceding 20-period RSI low. To avoid lookahead and head-fake style logic, the scan uses only negative Ref offsets and requires the current close above the upper band with the prior close not already above the prior upper band.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ColC &lt; ColD AND ColA &gt; ColB AND ColE &lt;= ColF AND ColE &lt; ColG AND ColI &gt; ColJ</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>[{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "BBandTop(C,20,S,2)"}, {"col_letter": "C", "col_code": "BBandTop(C,20,S,2)-BBandBot(C,20,S,2)"}, {"col_letter": "D", "col_code": "Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S)"}, {"col_letter": "E", "col_code": "Ref(C,-1)"}, {"col_letter": "F", "col_code": "Ref(BBandTop(C,20,S,2),-1)"}, {"col_letter": "G", "col_code": "Ref(LLV(C,20),-2)"}, {"col_letter": "H", "col_code": "RSI(14)"}, {"col_letter": "I", "col_code": "Ref(RSI(14),-1)"}, {"col_letter": "J", "col_code": "Ref(LLV(RSI(14),20),-2)"}]</t>
+        </is>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>["col G: Positive Ref(...,+N) / Ref(...,N) appears to reference future data. Use negative periods such as Ref(C,-1) for previous bars in Explorer.", "col J: Positive Ref(...,+N) / Ref(...,N) appears to reference future data. Use negative periods such as Ref(C,-1) for previous bars in Explorer."]</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>{"explorer_name": "BB Squeeze RSI Div Breakout", "explorer_description": "Finds stocks with a Bollinger Band squeeze and a close-confirmed breakout above the upper Bollinger Band. Assumptions: default Bollinger settings are C,20,S,2; squeeze means band width is below its 50-period simple average; RSI uses RSI(14); bullish RSI divergence is approximated with prior-bar fixed-window logic, where the prior close made a lower low versus the preceding 20-period close low while prior RSI stayed above its preceding 20-period RSI low. To avoid lookahead and head-fake style logic, the scan uses only negative Ref offsets and requires the current close above the upper band with the prior close not already above the prior upper band.", "explorer_code_body": "ColC &lt; ColD AND ColA &gt; ColB AND ColE &lt;= ColF AND ColE &lt; ColG AND ColI &gt; ColJ", "col_definitions": [{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "BBandTop(C,20,S,2)"}, {"col_letter": "C", "col_code": "BBandTop(C,20,S,2)-BBandBot(C,20,S,2)"}, {"col_letter": "D", "col_code": "Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S)"}, {"col_letter": "E", "col_code": "Ref(C,-1)"}, {"col_letter": "F", "col_code": "Ref(BBandTop(C,20,S,2),-1)"}, {"col_letter": "G", "col_code": "Ref(LLV(C,20),-2)"}, {"col_letter": "H", "col_code": "RSI(14)"}, {"col_letter": "I", "col_code": "Ref(RSI(14),-1)"}, {"col_letter": "J", "col_code": "Ref(LLV(RSI(14),20),-2)"}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-07T10:57:14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Find stocks where Bollinger Bands have contracted into a squeeze, price closes above the upper Bollinger Band, RSI shows bullish divergence, and the formula should avoid lookahead or head-fake style false breakout logic</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>BB Squeeze Breakout RSI Div</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Finds stocks with a Bollinger Band squeeze and bullish upper-band breakout. Assumptions: Bollinger Bands use C,20,S,2; squeeze means current band width is below its 50-period simple average; RSI uses RSI(14); bullish RSI divergence is approximated without lookahead as the current low below the previous 20-period low while RSI is above its previous 20-period low. To reduce head-fake style false breakouts, the filter requires close above the upper band and volume above its 20-period average. Only negative Ref() offsets are used.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>ColD &lt; ColE AND ColA &gt; ColB AND ColF &lt; ColG AND ColH &gt; ColI AND ColJ &gt; ColK</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>[{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "BBandTop(C,20,S,2)"}, {"col_letter": "C", "col_code": "BBandBot(C,20,S,2)"}, {"col_letter": "D", "col_code": "BBandTop(C,20,S,2)-BBandBot(C,20,S,2)"}, {"col_letter": "E", "col_code": "Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S)"}, {"col_letter": "F", "col_code": "L"}, {"col_letter": "G", "col_code": "Ref(LLV(L,20),-1)"}, {"col_letter": "H", "col_code": "RSI(14)"}, {"col_letter": "I", "col_code": "Ref(LLV(RSI(14),20),-1)"}, {"col_letter": "J", "col_code": "V"}, {"col_letter": "K", "col_code": "Mov(V,20,S)"}]</t>
+        </is>
+      </c>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>{"explorer_name": "BB Squeeze Breakout RSI Div", "explorer_description": "Finds stocks with a Bollinger Band squeeze and bullish upper-band breakout. Assumptions: Bollinger Bands use C,20,S,2; squeeze means current band width is below its 50-period simple average; RSI uses RSI(14); bullish RSI divergence is approximated without lookahead as the current low below the previous 20-period low while RSI is above its previous 20-period low. To reduce head-fake style false breakouts, the filter requires close above the upper band and volume above its 20-period average. Only negative Ref() offsets are used.", "explorer_code_body": "ColD &lt; ColE AND ColA &gt; ColB AND ColF &lt; ColG AND ColH &gt; ColI AND ColJ &gt; ColK", "col_definitions": [{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "BBandTop(C,20,S,2)"}, {"col_letter": "C", "col_code": "BBandBot(C,20,S,2)"}, {"col_letter": "D", "col_code": "BBandTop(C,20,S,2)-BBandBot(C,20,S,2)"}, {"col_letter": "E", "col_code": "Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S)"}, {"col_letter": "F", "col_code": "L"}, {"col_letter": "G", "col_code": "Ref(LLV(L,20),-1)"}, {"col_letter": "H", "col_code": "RSI(14)"}, {"col_letter": "I", "col_code": "Ref(LLV(RSI(14),20),-1)"}, {"col_letter": "J", "col_code": "V"}, {"col_letter": "K", "col_code": "Mov(V,20,S)"}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-07T10:59:28</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Find stocks where Bollinger Bands have contracted into a squeeze, price closes above the upper Bollinger Band, RSI shows bullish divergence, and the formula should avoid lookahead or head-fake style false breakout logic</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>BB Squeeze RSI Div Breakout</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Finds stocks with a Bollinger Band squeeze and a fresh close above the upper Bollinger Band, plus a fixed-window bullish RSI divergence approximation on the previous bar. Assumptions: Bollinger Bands use C,20,S,2; squeeze means band width is below its 50-period simple average; RSI uses RSI(14); bullish divergence uses a 20-period fixed lookback shifted to the prior bar to avoid future/lookahead or ZigZag repaint logic. The prior close must not already be above the prior upper band to reduce extended/head-fake style breakout logic.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>ColC &lt; ColD AND ColA &gt; ColB AND ColF &lt;= ColJ AND ColF &lt; ColG AND ColH &gt; ColI</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>[{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "BBandTop(C,20,S,2)"}, {"col_letter": "C", "col_code": "BBandTop(C,20,S,2)-BBandBot(C,20,S,2)"}, {"col_letter": "D", "col_code": "Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S)"}, {"col_letter": "E", "col_code": "RSI(14)"}, {"col_letter": "F", "col_code": "Ref(C,-1)"}, {"col_letter": "G", "col_code": "Ref(LLV(C,20),-2)"}, {"col_letter": "H", "col_code": "Ref(RSI(14),-1)"}, {"col_letter": "I", "col_code": "Ref(LLV(RSI(14),20),-2)"}, {"col_letter": "J", "col_code": "Ref(BBandTop(C,20,S,2),-1)"}]</t>
+        </is>
+      </c>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>{"explorer_name": "BB Squeeze RSI Div Breakout", "explorer_description": "Finds stocks with a Bollinger Band squeeze and a fresh close above the upper Bollinger Band, plus a fixed-window bullish RSI divergence approximation on the previous bar. Assumptions: Bollinger Bands use C,20,S,2; squeeze means band width is below its 50-period simple average; RSI uses RSI(14); bullish divergence uses a 20-period fixed lookback shifted to the prior bar to avoid future/lookahead or ZigZag repaint logic. The prior close must not already be above the prior upper band to reduce extended/head-fake style breakout logic.", "explorer_code_body": "ColC &lt; ColD AND ColA &gt; ColB AND ColF &lt;= ColJ AND ColF &lt; ColG AND ColH &gt; ColI", "col_definitions": [{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "BBandTop(C,20,S,2)"}, {"col_letter": "C", "col_code": "BBandTop(C,20,S,2)-BBandBot(C,20,S,2)"}, {"col_letter": "D", "col_code": "Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S)"}, {"col_letter": "E", "col_code": "RSI(14)"}, {"col_letter": "F", "col_code": "Ref(C,-1)"}, {"col_letter": "G", "col_code": "Ref(LLV(C,20),-2)"}, {"col_letter": "H", "col_code": "Ref(RSI(14),-1)"}, {"col_letter": "I", "col_code": "Ref(LLV(RSI(14),20),-2)"}, {"col_letter": "J", "col_code": "Ref(BBandTop(C,20,S,2),-1)"}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-07T11:01:33</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Find stocks where Bollinger Bands have contracted into a squeeze, price closes above the upper Bollinger Band, RSI shows bullish divergence, and the formula should avoid lookahead or head-fake style false breakout logic</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>BB Squeeze RSI Div Breakout</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Finds bullish Bollinger squeeze breakouts where current band width is below its 50-period average, the close is above the upper Bollinger Band, and bullish RSI divergence is approximated using the prior completed bar to avoid lookahead. Assumes default Bollinger settings C,20,S,2; RSI(14); a 20-period fixed-window divergence approximation; and volume above 20-period average as confirmation to reduce head-fake breakout risk.</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>(BBandTop(C,20,S,2)-BBandBot(C,20,S,2)) &lt; Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S) AND C &gt; BBandTop(C,20,S,2) AND Ref(C,-1) &lt; Ref(LLV(C,20),-2) AND Ref(RSI(14),-1) &gt; Ref(LLV(RSI(14),20),-2) AND V &gt; Mov(V,20,S)</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>[{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "BBandTop(C,20,S,2)"}, {"col_letter": "C", "col_code": "BBandBot(C,20,S,2)"}, {"col_letter": "D", "col_code": "BBandTop(C,20,S,2)-BBandBot(C,20,S,2)"}, {"col_letter": "E", "col_code": "Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S)"}, {"col_letter": "F", "col_code": "RSI(14)"}, {"col_letter": "G", "col_code": "Ref(C,-1)"}, {"col_letter": "H", "col_code": "Ref(LLV(C,20),-2)"}, {"col_letter": "I", "col_code": "Ref(RSI(14),-1)"}, {"col_letter": "J", "col_code": "Ref(LLV(RSI(14),20),-2)"}, {"col_letter": "K", "col_code": "V"}, {"col_letter": "L", "col_code": "Mov(V,20,S)"}]</t>
+        </is>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>{"explorer_name": "BB Squeeze RSI Div Breakout", "explorer_description": "Finds bullish Bollinger squeeze breakouts where current band width is below its 50-period average, the close is above the upper Bollinger Band, and bullish RSI divergence is approximated using the prior completed bar to avoid lookahead. Assumes default Bollinger settings C,20,S,2; RSI(14); a 20-period fixed-window divergence approximation; and volume above 20-period average as confirmation to reduce head-fake breakout risk.", "explorer_code_body": "(BBandTop(C,20,S,2)-BBandBot(C,20,S,2)) &lt; Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S) AND C &gt; BBandTop(C,20,S,2) AND Ref(C,-1) &lt; Ref(LLV(C,20),-2) AND Ref(RSI(14),-1) &gt; Ref(LLV(RSI(14),20),-2) AND V &gt; Mov(V,20,S)", "col_definitions": [{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "BBandTop(C,20,S,2)"}, {"col_letter": "C", "col_code": "BBandBot(C,20,S,2)"}, {"col_letter": "D", "col_code": "BBandTop(C,20,S,2)-BBandBot(C,20,S,2)"}, {"col_letter": "E", "col_code": "Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S)"}, {"col_letter": "F", "col_code": "RSI(14)"}, {"col_letter": "G", "col_code": "Ref(C,-1)"}, {"col_letter": "H", "col_code": "Ref(LLV(C,20),-2)"}, {"col_letter": "I", "col_code": "Ref(RSI(14),-1)"}, {"col_letter": "J", "col_code": "Ref(LLV(RSI(14),20),-2)"}, {"col_letter": "K", "col_code": "V"}, {"col_letter": "L", "col_code": "Mov(V,20,S)"}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-07T11:05:08</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Find stocks where Bollinger Bands have contracted into a squeeze, price closes above the upper Bollinger Band, RSI shows bullish divergence, and the formula should avoid lookahead or head-fake style false breakout logic</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>BB Squeeze RSI Div Breakout</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Finds stocks with a Bollinger Band squeeze and a close-confirmed breakout above the upper Bollinger Band, while also requiring a fixed-window bullish RSI divergence approximation. Assumptions: Bollinger Bands use C,20,S,2; squeeze means current band width is below its 50-period simple average; RSI uses 14 periods; bullish divergence is checked on the prior completed bar by requiring the prior close to be below its previous 20-period low while prior RSI is above its previous 20-period RSI low. This avoids future references and avoids ZigZag/Divergence-function repaint risk; using the close above the upper band helps avoid intrabar head-fake breakout logic.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>(BBandTop(C,20,S,2)-BBandBot(C,20,S,2)) &lt; Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S) AND C &gt; BBandTop(C,20,S,2) AND Ref(C,-1) &lt; Ref(LLV(C,20),-2) AND Ref(RSI(14),-1) &gt; Ref(LLV(RSI(14),20),-2)</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>[{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "BBandTop(C,20,S,2)"}, {"col_letter": "C", "col_code": "BBandBot(C,20,S,2)"}, {"col_letter": "D", "col_code": "BBandTop(C,20,S,2)-BBandBot(C,20,S,2)"}, {"col_letter": "E", "col_code": "Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S)"}, {"col_letter": "F", "col_code": "Ref(C,-1)"}, {"col_letter": "G", "col_code": "Ref(LLV(C,20),-2)"}, {"col_letter": "H", "col_code": "Ref(RSI(14),-1)"}, {"col_letter": "I", "col_code": "Ref(LLV(RSI(14),20),-2)"}, {"col_letter": "J", "col_code": "RSI(14)"}]</t>
+        </is>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>{"explorer_name": "BB Squeeze RSI Div Breakout", "explorer_description": "Finds stocks with a Bollinger Band squeeze and a close-confirmed breakout above the upper Bollinger Band, while also requiring a fixed-window bullish RSI divergence approximation. Assumptions: Bollinger Bands use C,20,S,2; squeeze means current band width is below its 50-period simple average; RSI uses 14 periods; bullish divergence is checked on the prior completed bar by requiring the prior close to be below its previous 20-period low while prior RSI is above its previous 20-period RSI low. This avoids future references and avoids ZigZag/Divergence-function repaint risk; using the close above the upper band helps avoid intrabar head-fake breakout logic.", "explorer_code_body": "(BBandTop(C,20,S,2)-BBandBot(C,20,S,2)) &lt; Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S) AND C &gt; BBandTop(C,20,S,2) AND Ref(C,-1) &lt; Ref(LLV(C,20),-2) AND Ref(RSI(14),-1) &gt; Ref(LLV(RSI(14),20),-2)", "col_definitions": [{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "BBandTop(C,20,S,2)"}, {"col_letter": "C", "col_code": "BBandBot(C,20,S,2)"}, {"col_letter": "D", "col_code": "BBandTop(C,20,S,2)-BBandBot(C,20,S,2)"}, {"col_letter": "E", "col_code": "Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S)"}, {"col_letter": "F", "col_code": "Ref(C,-1)"}, {"col_letter": "G", "col_code": "Ref(LLV(C,20),-2)"}, {"col_letter": "H", "col_code": "Ref(RSI(14),-1)"}, {"col_letter": "I", "col_code": "Ref(LLV(RSI(14),20),-2)"}, {"col_letter": "J", "col_code": "RSI(14)"}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-07T11:09:10</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Find stocks where Bollinger Bands have contracted into a squeeze, price closes above the upper Bollinger Band, RSI shows bullish divergence, and the formula should avoid lookahead or head-fake style false breakout logic</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>BB Squeeze RSI Div Breakout</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Finds bullish Bollinger Band squeeze breakouts using default Bollinger settings C,20,S,2 and default RSI(14). Assumes squeeze means the prior bar's band width was below its prior 50-period average width. Bullish RSI divergence is approximated without lookahead as the prior bar making a lower 20-period close low while prior RSI stayed above its prior 20-period RSI low. To reduce head-fake style false breakouts without using future bars, the scan requires current close above the upper band plus current volume above its 20-period simple average.</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ColC &lt; ColD AND ColA &gt; ColB AND ColE &lt; ColF AND ColG &gt; ColH AND ColI &gt; ColJ</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>[{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "BBandTop(C,20,S,2)"}, {"col_letter": "C", "col_code": "Ref(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),-1)"}, {"col_letter": "D", "col_code": "Ref(Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S),-1)"}, {"col_letter": "E", "col_code": "Ref(C,-1)"}, {"col_letter": "F", "col_code": "Ref(LLV(C,20),-2)"}, {"col_letter": "G", "col_code": "Ref(RSI(14),-1)"}, {"col_letter": "H", "col_code": "Ref(LLV(RSI(14),20),-2)"}, {"col_letter": "I", "col_code": "V"}, {"col_letter": "J", "col_code": "Mov(V,20,S)"}]</t>
+        </is>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>{"explorer_name": "BB Squeeze RSI Div Breakout", "explorer_description": "Finds bullish Bollinger Band squeeze breakouts using default Bollinger settings C,20,S,2 and default RSI(14). Assumes squeeze means the prior bar's band width was below its prior 50-period average width. Bullish RSI divergence is approximated without lookahead as the prior bar making a lower 20-period close low while prior RSI stayed above its prior 20-period RSI low. To reduce head-fake style false breakouts without using future bars, the scan requires current close above the upper band plus current volume above its 20-period simple average.", "explorer_code_body": "ColC &lt; ColD AND ColA &gt; ColB AND ColE &lt; ColF AND ColG &gt; ColH AND ColI &gt; ColJ", "col_definitions": [{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "BBandTop(C,20,S,2)"}, {"col_letter": "C", "col_code": "Ref(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),-1)"}, {"col_letter": "D", "col_code": "Ref(Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S),-1)"}, {"col_letter": "E", "col_code": "Ref(C,-1)"}, {"col_letter": "F", "col_code": "Ref(LLV(C,20),-2)"}, {"col_letter": "G", "col_code": "Ref(RSI(14),-1)"}, {"col_letter": "H", "col_code": "Ref(LLV(RSI(14),20),-2)"}, {"col_letter": "I", "col_code": "V"}, {"col_letter": "J", "col_code": "Mov(V,20,S)"}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-07T11:33:37</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Find stocks where Bollinger Bands have contracted into a squeeze, price closes above the upper Bollinger Band, RSI shows bullish divergence, and the formula should avoid lookahead or head-fake style false breakout logic</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>BB Squeeze Breakout RSI Div</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Finds stocks where Bollinger Bands had a prior-bar squeeze, today's close is above the upper Bollinger Band, the prior bar showed a fixed-window bullish RSI divergence approximation, and volume is above its 20-period average to help reduce head-fake breakouts. Assumes default Bollinger settings C,20,S,2, RSI(14), a 20-period divergence lookback, and a 50-period average band-width comparison. Uses only negative Ref offsets to avoid lookahead.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>ColC &lt; ColD AND ColA &gt; ColB AND ColE &lt; ColF AND ColG &gt; ColH AND ColI &gt; ColJ</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>[{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "BBandTop(C,20,S,2)"}, {"col_letter": "C", "col_code": "Ref(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),-1)"}, {"col_letter": "D", "col_code": "Ref(Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S),-1)"}, {"col_letter": "E", "col_code": "Ref(C,-1)"}, {"col_letter": "F", "col_code": "Ref(LLV(C,20),-2)"}, {"col_letter": "G", "col_code": "Ref(RSI(14),-1)"}, {"col_letter": "H", "col_code": "Ref(LLV(RSI(14),20),-2)"}, {"col_letter": "I", "col_code": "V"}, {"col_letter": "J", "col_code": "Mov(V,20,S)"}]</t>
+        </is>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>{"explorer_name": "BB Squeeze Breakout RSI Div", "explorer_description": "Finds stocks where Bollinger Bands had a prior-bar squeeze, today's close is above the upper Bollinger Band, the prior bar showed a fixed-window bullish RSI divergence approximation, and volume is above its 20-period average to help reduce head-fake breakouts. Assumes default Bollinger settings C,20,S,2, RSI(14), a 20-period divergence lookback, and a 50-period average band-width comparison. Uses only negative Ref offsets to avoid lookahead.", "explorer_code_body": "ColC &lt; ColD AND ColA &gt; ColB AND ColE &lt; ColF AND ColG &gt; ColH AND ColI &gt; ColJ", "col_definitions": [{"col_letter": "A", "col_code": "C"}, {"col_letter": "B", "col_code": "BBandTop(C,20,S,2)"}, {"col_letter": "C", "col_code": "Ref(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),-1)"}, {"col_letter": "D", "col_code": "Ref(Mov(BBandTop(C,20,S,2)-BBandBot(C,20,S,2),50,S),-1)"}, {"col_letter": "E", "col_code": "Ref(C,-1)"}, {"col_letter": "F", "col_code": "Ref(LLV(C,20),-2)"}, {"col_letter": "G", "col_code": "Ref(RSI(14),-1)"}, {"col_letter": "H", "col_code": "Ref(LLV(RSI(14),20),-2)"}, {"col_letter": "I", "col_code": "V"}, {"col_letter": "J", "col_code": "Mov(V,20,S)"}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-07T12:11:25</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>locate stocks that are RSI oversold and Stochastic oversold, crossing upwards from the lows. volume needs to be greater than moving average volume for the past 1 year. find stocks that fulfill this criteria with a lookback period of 5 days.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RSI Stoch 5 Day Recovery</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Finds stocks where RSI(14) crossed upward through the oversold recovery level of 30 within the last 5 bars, Stoch(14,3) crossed upward through the oversold recovery level of 20 within the last 5 bars, and current volume is greater than its 1-year average volume. Assumes 1 trading year is 252 periods and the lookback period of 5 days means the crossing events occurred within the last 5 bars.</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>ColE AND ColF AND ColC &gt; ColD</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>[{"col_letter": "A", "col_code": "RSI(14)"}, {"col_letter": "B", "col_code": "Stoch(14,3)"}, {"col_letter": "C", "col_code": "V"}, {"col_letter": "D", "col_code": "Mov(V,252,S)"}, {"col_letter": "E", "col_code": "Cross(RSI(14),30) OR Ref(Cross(RSI(14),30),-1) OR Ref(Cross(RSI(14),30),-2) OR Ref(Cross(RSI(14),30),-3) OR Ref(Cross(RSI(14),30),-4)"}, {"col_letter": "F", "col_code": "Cross(Stoch(14,3),20) OR Ref(Cross(Stoch(14,3),20),-1) OR Ref(Cross(Stoch(14,3),20),-2) OR Ref(Cross(Stoch(14,3),20),-3) OR Ref(Cross(Stoch(14,3),20),-4)"}]</t>
+        </is>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>{"explorer_name": "RSI Stoch 5 Day Recovery", "explorer_description": "Finds stocks where RSI(14) crossed upward through the oversold recovery level of 30 within the last 5 bars, Stoch(14,3) crossed upward through the oversold recovery level of 20 within the last 5 bars, and current volume is greater than its 1-year average volume. Assumes 1 trading year is 252 periods and the lookback period of 5 days means the crossing events occurred within the last 5 bars.", "explorer_code_body": "ColE AND ColF AND ColC &gt; ColD", "col_definitions": [{"col_letter": "A", "col_code": "RSI(14)"}, {"col_letter": "B", "col_code": "Stoch(14,3)"}, {"col_letter": "C", "col_code": "V"}, {"col_letter": "D", "col_code": "Mov(V,252,S)"}, {"col_letter": "E", "col_code": "Cross(RSI(14),30) OR Ref(Cross(RSI(14),30),-1) OR Ref(Cross(RSI(14),30),-2) OR Ref(Cross(RSI(14),30),-3) OR Ref(Cross(RSI(14),30),-4)"}, {"col_letter": "F", "col_code": "Cross(Stoch(14,3),20) OR Ref(Cross(Stoch(14,3),20),-1) OR Ref(Cross(Stoch(14,3),20),-2) OR Ref(Cross(Stoch(14,3),20),-3) OR Ref(Cross(Stoch(14,3),20),-4)"}]}</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-07T12:28:29</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>openai</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>gpt-5.5</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>find stocks that exhibit the scenario where we can identify 3 or more lows and such lows must form a straight line that adopts y=mx+c. Allowance can be given such that the y=mx+c to not be strictly straight. these recent lows must take place over a period of 2 years. the stock must be currently at a low that is +/- 3% from an expected upcoming low, interpolating from the striaght line derived.</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>3 Low Trendline Test</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Finds stocks where the last three ZigZag-style lows approximate a straight support line over the last two years, assumed as 504 trading bars. Because no ZigZag swing size was specified, this uses 5% Trough/TroughBars lows. The middle low must be within +/-3% of the line between the oldest and most recent trough, and the current low must be within +/-3% of the extrapolated current support value. Trough-based signals can repaint as new data arrives.</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>ColB &gt; 0 AND ColC &gt; 0 AND ColD &gt; 0 AND ColG &lt;= 504 AND ColG &gt; ColF AND ColF &gt; ColE AND ColC &gt;= ColI * 0.97 AND ColC &lt;= ColI * 1.03 AND ColA &gt;= ColH * 0.97 AND ColA &lt;= ColH * 1.03</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>[{"col_letter": "A", "col_code": "L"}, {"col_letter": "B", "col_code": "Trough(1,L,5)"}, {"col_letter": "C", "col_code": "Trough(2,L,5)"}, {"col_letter": "D", "col_code": "Trough(3,L,5)"}, {"col_letter": "E", "col_code": "TroughBars(1,L,5)"}, {"col_letter": "F", "col_code": "TroughBars(2,L,5)"}, {"col_letter": "G", "col_code": "TroughBars(3,L,5)"}, {"col_letter": "H", "col_code": "Trough(1,L,5) + TroughBars(1,L,5) * (Trough(1,L,5) - Trough(3,L,5)) / (TroughBars(3,L,5) - TroughBars(1,L,5))"}, {"col_letter": "I", "col_code": "Trough(3,L,5) + (TroughBars(3,L,5) - TroughBars(2,L,5)) * (Trough(1,L,5) - Trough(3,L,5)) / (TroughBars(3,L,5) - TroughBars(1,L,5))"}, {"col_letter": "J", "col_code": "100 * (L - (Trough(1,L,5) + TroughBars(1,L,5) * (Trough(1,L,5) - Trough(3,L,5)) / (TroughBars(3,L,5) - TroughBars(1,L,5)))) / (Trough(1,L,5) + TroughBars(1,L,5) * (Trough(1,L,5) - Trough(3,L,5)) / (TroughBars(3,L,5) - TroughBars(1,L,5)))"}]</t>
+        </is>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>{"explorer_name": "3 Low Trendline Test", "explorer_description": "Finds stocks where the last three ZigZag-style lows approximate a straight support line over the last two years, assumed as 504 trading bars. Because no ZigZag swing size was specified, this uses 5% Trough/TroughBars lows. The middle low must be within +/-3% of the line between the oldest and most recent trough, and the current low must be within +/-3% of the extrapolated current support value. Trough-based signals can repaint as new data arrives.", "explorer_code_body": "ColB &gt; 0 AND ColC &gt; 0 AND ColD &gt; 0 AND ColG &lt;= 504 AND ColG &gt; ColF AND ColF &gt; ColE AND ColC &gt;= ColI * 0.97 AND ColC &lt;= ColI * 1.03 AND ColA &gt;= ColH * 0.97 AND ColA &lt;= ColH * 1.03", "col_definitions": [{"col_letter": "A", "col_code": "L"}, {"col_letter": "B", "col_code": "Trough(1,L,5)"}, {"col_letter": "C", "col_code": "Trough(2,L,5)"}, {"col_letter": "D", "col_code": "Trough(3,L,5)"}, {"col_letter": "E", "col_code": "TroughBars(1,L,5)"}, {"col_letter": "F", "col_code": "TroughBars(2,L,5)"}, {"col_letter": "G", "col_code": "TroughBars(3,L,5)"}, {"col_letter": "H", "col_code": "Trough(1,L,5) + TroughBars(1,L,5) * (Trough(1,L,5) - Trough(3,L,5)) / (TroughBars(3,L,5) - TroughBars(1,L,5))"}, {"col_letter": "I", "col_code": "Trough(3,L,5) + (TroughBars(3,L,5) - TroughBars(2,L,5)) * (Trough(1,L,5) - Trough(3,L,5)) / (TroughBars(3,L,5) - TroughBars(1,L,5))"}, {"col_letter": "J", "col_code": "100 * (L - (Trough(1,L,5) + TroughBars(1,L,5) * (Trough(1,L,5) - Trough(3,L,5)) / (TroughBars(3,L,5) - TroughBars(1,L,5)))) / (Trough(1,L,5) + TroughBars(1,L,5) * (Trough(1,L,5) - Trough(3,L,5)) / (TroughBars(3,L,5) - TroughBars(1,L,5)))"}]}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
